--- a/escala_limpeza_13_09_2026.xlsx
+++ b/escala_limpeza_13_09_2026.xlsx
@@ -56,7 +56,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FF0000"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -66,7 +66,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00FF0000"/>
       </patternFill>
     </fill>
     <fill>
@@ -530,13 +530,13 @@
           <t>JUKEBOX</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr"/>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>Sala e copa</t>
+        </is>
+      </c>
       <c r="C3" s="6" t="inlineStr"/>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>Armários cozinha</t>
-        </is>
-      </c>
+      <c r="D3" s="7" t="inlineStr"/>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -544,13 +544,13 @@
           <t>LOTERYA</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Geladeira</t>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Cozinha</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
+      <c r="D4" s="7" t="inlineStr"/>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -558,15 +558,15 @@
           <t>KOMIXÃO</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Panos</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr"/>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Área traseira da casa</t>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Garagem</t>
         </is>
       </c>
     </row>
@@ -576,13 +576,13 @@
           <t>NAMOITA</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Lavanderia</t>
-        </is>
-      </c>
+      <c r="B6" s="7" t="inlineStr"/>
       <c r="C6" s="6" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Armários cozinha</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -590,15 +590,15 @@
           <t>NAZARÉ</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>Área frontal da casa</t>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Geladeira</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>Sala e copa</t>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Área traseira da casa</t>
         </is>
       </c>
     </row>
@@ -608,13 +608,13 @@
           <t>CAMILA</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Área frontal da casa</t>
+        </is>
+      </c>
       <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>Cozinha</t>
-        </is>
-      </c>
+      <c r="D8" s="7" t="inlineStr"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -622,13 +622,13 @@
           <t>BAQUETADA</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr"/>
+      <c r="C9" s="6" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Cozinha</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="5" t="inlineStr"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -654,15 +654,15 @@
           <t>BELA</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Lavanderia</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr"/>
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Sala e copa</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr"/>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>Garagem</t>
         </is>
       </c>
     </row>

--- a/escala_limpeza_13_09_2026.xlsx
+++ b/escala_limpeza_13_09_2026.xlsx
@@ -532,7 +532,7 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Sala e copa</t>
+          <t>Lavanderia</t>
         </is>
       </c>
       <c r="C3" s="6" t="inlineStr"/>
@@ -544,13 +544,13 @@
           <t>LOTERYA</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Cozinha</t>
-        </is>
-      </c>
+      <c r="B4" s="7" t="inlineStr"/>
       <c r="C4" s="6" t="inlineStr"/>
-      <c r="D4" s="7" t="inlineStr"/>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Área traseira da casa</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -564,11 +564,7 @@
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Garagem</t>
-        </is>
-      </c>
+      <c r="D5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -580,7 +576,7 @@
       <c r="C6" s="6" t="inlineStr"/>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Armários cozinha</t>
+          <t>Cozinha</t>
         </is>
       </c>
     </row>
@@ -592,13 +588,13 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Geladeira</t>
+          <t>Cozinha</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr"/>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Área traseira da casa</t>
+          <t>Garagem</t>
         </is>
       </c>
     </row>
@@ -614,7 +610,11 @@
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="7" t="inlineStr"/>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Sala e copa</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -622,13 +622,13 @@
           <t>BAQUETADA</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Geladeira</t>
+        </is>
+      </c>
       <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Cozinha</t>
-        </is>
-      </c>
+      <c r="D9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -656,13 +656,13 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Lavanderia</t>
+          <t>Sala e copa</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr"/>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Sala e copa</t>
+          <t>Armários cozinha</t>
         </is>
       </c>
     </row>

--- a/escala_limpeza_13_09_2026.xlsx
+++ b/escala_limpeza_13_09_2026.xlsx
@@ -56,7 +56,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00FF0000"/>
       </patternFill>
     </fill>
     <fill>
@@ -66,7 +66,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FF0000"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -530,13 +530,13 @@
           <t>JUKEBOX</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Lavanderia</t>
-        </is>
-      </c>
+      <c r="B3" s="5" t="inlineStr"/>
       <c r="C3" s="6" t="inlineStr"/>
-      <c r="D3" s="7" t="inlineStr"/>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Sala e copa</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
@@ -544,11 +544,11 @@
           <t>LOTERYA</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr"/>
+      <c r="B4" s="5" t="inlineStr"/>
       <c r="C4" s="6" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Área traseira da casa</t>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Garagem</t>
         </is>
       </c>
     </row>
@@ -558,13 +558,17 @@
           <t>KOMIXÃO</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Panos</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr"/>
-      <c r="D5" s="7" t="inlineStr"/>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Área traseira da casa</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
@@ -572,13 +576,13 @@
           <t>NAMOITA</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr"/>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Lavanderia</t>
+        </is>
+      </c>
       <c r="C6" s="6" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>Cozinha</t>
-        </is>
-      </c>
+      <c r="D6" s="5" t="inlineStr"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
@@ -586,15 +590,15 @@
           <t>NAZARÉ</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Cozinha</t>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Sala e copa</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Garagem</t>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>Armários cozinha</t>
         </is>
       </c>
     </row>
@@ -604,17 +608,13 @@
           <t>CAMILA</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Área frontal da casa</t>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Cozinha</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Sala e copa</t>
-        </is>
-      </c>
+      <c r="D8" s="5" t="inlineStr"/>
     </row>
     <row r="9" ht="22" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
@@ -622,13 +622,13 @@
           <t>BAQUETADA</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Geladeira</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="7" t="inlineStr"/>
+      <c r="D9" s="5" t="inlineStr"/>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
@@ -654,15 +654,15 @@
           <t>BELA</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Sala e copa</t>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Área frontal da casa</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Armários cozinha</t>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Cozinha</t>
         </is>
       </c>
     </row>

--- a/escala_limpeza_13_09_2026.xlsx
+++ b/escala_limpeza_13_09_2026.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Lavanderia</t>
+          <t>Área frontal da casa</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr"/>
@@ -598,7 +598,7 @@
       <c r="C7" s="6" t="inlineStr"/>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Armários cozinha</t>
+          <t>Cozinha</t>
         </is>
       </c>
     </row>
@@ -656,13 +656,13 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Área frontal da casa</t>
+          <t>Lavanderia</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr"/>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>Cozinha</t>
+          <t>Armários cozinha</t>
         </is>
       </c>
     </row>
